--- a/ssp_modeling/input_data/reference/Libya_Water_Energy_Model_2026_04_24.xlsx
+++ b/ssp_modeling/input_data/reference/Libya_Water_Energy_Model_2026_04_24.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{95BCF2D9-855F-3C40-9D93-B04089B131D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-960" yWindow="660" windowWidth="27740" windowHeight="18980" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1554,16 +1554,16 @@
     <xf numFmtId="165" fontId="7" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="17" fillId="15" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14321,12 +14321,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -14343,12 +14343,12 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
@@ -14419,12 +14419,12 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="89" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
@@ -14512,12 +14512,12 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="89" t="s">
         <v>146</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
@@ -14579,12 +14579,12 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="89" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
     </row>
     <row r="26" spans="1:5" ht="98" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
@@ -14672,12 +14672,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90" t="s">
+      <c r="A33" s="89" t="s">
         <v>169</v>
       </c>
-      <c r="B33" s="88"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="90"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
@@ -14758,7 +14758,7 @@
       <c r="A41" t="s">
         <v>183</v>
       </c>
-      <c r="B41" s="91">
+      <c r="B41" s="87">
         <v>0.01</v>
       </c>
       <c r="C41" t="s">
@@ -14772,7 +14772,7 @@
       <c r="A42" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="91">
+      <c r="B42" s="87">
         <f>0.35*0.1</f>
         <v>3.4999999999999996E-2</v>
       </c>
@@ -22299,35 +22299,35 @@
       <c r="C12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="88">
         <f>D7*Supply!D31</f>
         <v>0</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="88">
         <f>E7*Supply!E31</f>
         <v>0</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="88">
         <f>F7*Supply!F31</f>
         <v>0</v>
       </c>
-      <c r="G12" s="92">
+      <c r="G12" s="88">
         <f>G7*Supply!G31</f>
         <v>0</v>
       </c>
-      <c r="H12" s="92">
+      <c r="H12" s="88">
         <f>H7*Supply!H31</f>
         <v>0</v>
       </c>
-      <c r="I12" s="92">
+      <c r="I12" s="88">
         <f>I7*Supply!I31</f>
         <v>0</v>
       </c>
-      <c r="J12" s="92">
+      <c r="J12" s="88">
         <f>J7*Supply!J31</f>
         <v>0</v>
       </c>
-      <c r="K12" s="92">
+      <c r="K12" s="88">
         <f>K7*Supply!K31</f>
         <v>158.19005123819849</v>
       </c>
@@ -25061,13 +25061,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="91" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -26332,11 +26332,11 @@
       </c>
     </row>
     <row r="120" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B120" s="89"/>
-      <c r="C120" s="89"/>
-      <c r="D120" s="89"/>
-      <c r="E120" s="89"/>
-      <c r="F120" s="89"/>
+      <c r="B120" s="92"/>
+      <c r="C120" s="92"/>
+      <c r="D120" s="92"/>
+      <c r="E120" s="92"/>
+      <c r="F120" s="92"/>
       <c r="J120" t="s">
         <v>355</v>
       </c>
